--- a/KIJ/CO_Ar/VLE_CO_Ar.xlsx
+++ b/KIJ/CO_Ar/VLE_CO_Ar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\darshanraju\OneDrive - Delft University of Technology\Desktop\A6\KIJ\CO_Ar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2915D6-71F0-4A6A-8AD0-9B48BAE20B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2CCC2E4-8789-4B17-B3DC-A0B07947F3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,13 +53,13 @@
     <t>source</t>
   </si>
   <si>
-    <t>Christiansen, L. J.; Fredenslund, A.; Mollerup, J. M. Cryogenics, 1973, 13, 405 Vapor-liquid equilibrium of the methane - argon, methane - carbon monoxide, and argon - carbon monoxide systems at elevated pressures</t>
-  </si>
-  <si>
     <t>CO</t>
   </si>
   <si>
     <t>Comp</t>
+  </si>
+  <si>
+    <t>Christiansen et al, (1973)</t>
   </si>
 </sst>
 </file>
@@ -438,7 +438,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -455,10 +455,10 @@
         <v>123.41330000000001</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -475,10 +475,10 @@
         <v>123.41330000000001</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -495,10 +495,10 @@
         <v>123.41330000000001</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -515,10 +515,10 @@
         <v>123.41330000000001</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -535,10 +535,10 @@
         <v>123.41330000000001</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -555,10 +555,10 @@
         <v>123.41330000000001</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -575,10 +575,10 @@
         <v>123.41330000000001</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -595,10 +595,10 @@
         <v>123.41330000000001</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -615,10 +615,10 @@
         <v>123.41330000000001</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -635,10 +635,10 @@
         <v>137.114</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -655,10 +655,10 @@
         <v>137.114</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -675,10 +675,10 @@
         <v>137.114</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -695,10 +695,10 @@
         <v>137.114</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -715,10 +715,10 @@
         <v>137.114</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -735,10 +735,10 @@
         <v>137.114</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -755,10 +755,10 @@
         <v>137.114</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
